--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-04-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6706EDC0-08E9-472E-925D-44C7208036B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E51F51-0EC1-43B9-9846-75B12F3D4955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4170" yWindow="2505" windowWidth="21600" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1733,7 +1733,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>63</v>
